--- a/class test/class test 12/CT TEST RECORD 2026.xlsx
+++ b/class test/class test 12/CT TEST RECORD 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 12/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="102" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5A58C513-568C-4BAD-98EE-9E5E57F9BA15}"/>
+  <xr:revisionPtr revIDLastSave="129" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E1FC7A3-4D95-46B3-A549-BF8DB697DE39}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="45">
   <si>
     <t>PM SHRI KV RANIKHET</t>
   </si>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t>MT-4</t>
+  </si>
+  <si>
+    <t>Ch10</t>
   </si>
 </sst>
 </file>
@@ -214,10 +217,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -542,7 +541,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
@@ -553,17 +552,17 @@
     <col min="12" max="13" width="6.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="43" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="43" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -603,8 +602,11 @@
       <c r="N3" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
@@ -644,8 +646,11 @@
       <c r="N4" s="1">
         <v>46266</v>
       </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O4" s="1">
+        <v>46276</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>42</v>
       </c>
@@ -685,13 +690,16 @@
       <c r="N5">
         <v>20</v>
       </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1</v>
       </c>
@@ -734,8 +742,11 @@
       <c r="N7">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2</v>
       </c>
@@ -778,8 +789,11 @@
       <c r="N8">
         <v>13</v>
       </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O8">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3</v>
       </c>
@@ -822,8 +836,11 @@
       <c r="N9">
         <v>12</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>4</v>
       </c>
@@ -866,8 +883,11 @@
       <c r="N10">
         <v>14</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>5</v>
       </c>
@@ -910,8 +930,11 @@
       <c r="N11">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>6</v>
       </c>
@@ -954,8 +977,11 @@
       <c r="N12">
         <v>19</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>7</v>
       </c>
@@ -998,8 +1024,11 @@
       <c r="N13">
         <v>10</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>8</v>
       </c>
@@ -1042,8 +1071,11 @@
       <c r="N14">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>9</v>
       </c>
@@ -1086,8 +1118,11 @@
       <c r="N15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>10</v>
       </c>
@@ -1130,8 +1165,11 @@
       <c r="N16">
         <v>14</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>11</v>
       </c>
@@ -1174,8 +1212,11 @@
       <c r="N17">
         <v>8</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>12</v>
       </c>
@@ -1218,8 +1259,11 @@
       <c r="N18">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O18">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>13</v>
       </c>
@@ -1262,8 +1306,11 @@
       <c r="N19">
         <v>13</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>14</v>
       </c>
@@ -1306,8 +1353,11 @@
       <c r="N20">
         <v>10</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>15</v>
       </c>
@@ -1350,8 +1400,11 @@
       <c r="N21">
         <v>7</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O21">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>16</v>
       </c>
@@ -1394,8 +1447,11 @@
       <c r="N22">
         <v>9</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O22" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>17</v>
       </c>
@@ -1438,8 +1494,11 @@
       <c r="N23">
         <v>10</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O23">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>18</v>
       </c>
@@ -1482,8 +1541,11 @@
       <c r="N24">
         <v>9</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O24">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>19</v>
       </c>
@@ -1526,8 +1588,11 @@
       <c r="N25">
         <v>14</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>20</v>
       </c>
@@ -1570,8 +1635,11 @@
       <c r="N26">
         <v>7</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>21</v>
       </c>
@@ -1614,8 +1682,11 @@
       <c r="N27">
         <v>18</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O27">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>22</v>
       </c>
@@ -1658,8 +1729,11 @@
       <c r="N28">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O28">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>23</v>
       </c>
@@ -1702,8 +1776,11 @@
       <c r="N29">
         <v>13</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O29">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>24</v>
       </c>
@@ -1727,6 +1804,9 @@
       </c>
       <c r="N30">
         <v>9</v>
+      </c>
+      <c r="O30">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/class test/class test 12/CT TEST RECORD 2026.xlsx
+++ b/class test/class test 12/CT TEST RECORD 2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1cf1c6ba2bb8aab4/Desktop/mydiarykv/class test/class test 12/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E1FC7A3-4D95-46B3-A549-BF8DB697DE39}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{6429252B-2373-4501-BE9C-E65E8DEA8152}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E2826BE-2D4E-41B6-842A-47B1A04B8AA9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="46">
   <si>
     <t>PM SHRI KV RANIKHET</t>
   </si>
@@ -158,6 +158,9 @@
   </si>
   <si>
     <t>Ch10</t>
+  </si>
+  <si>
+    <t>MT 5</t>
   </si>
 </sst>
 </file>
@@ -217,6 +220,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -541,7 +548,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O30"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="17.08203125" bestFit="1" customWidth="1"/>
@@ -552,17 +559,17 @@
     <col min="12" max="13" width="6.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="43" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="43" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -605,8 +612,11 @@
       <c r="O3" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
@@ -649,8 +659,11 @@
       <c r="O4" s="1">
         <v>46276</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P4" s="1">
+        <v>46293</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B5" s="3" t="s">
         <v>42</v>
       </c>
@@ -693,13 +706,16 @@
       <c r="O5">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P5">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>1</v>
       </c>
@@ -745,8 +761,11 @@
       <c r="O7">
         <v>2</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P7">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>2</v>
       </c>
@@ -792,8 +811,11 @@
       <c r="O8">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P8">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>3</v>
       </c>
@@ -839,8 +861,11 @@
       <c r="O9">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P9">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>4</v>
       </c>
@@ -886,8 +911,11 @@
       <c r="O10" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>5</v>
       </c>
@@ -933,8 +961,11 @@
       <c r="O11">
         <v>6</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P11">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>6</v>
       </c>
@@ -980,8 +1011,11 @@
       <c r="O12">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P12">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>7</v>
       </c>
@@ -1027,8 +1061,11 @@
       <c r="O13">
         <v>8</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P13">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>8</v>
       </c>
@@ -1074,8 +1111,11 @@
       <c r="O14">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>9</v>
       </c>
@@ -1121,8 +1161,11 @@
       <c r="O15">
         <v>5</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>10</v>
       </c>
@@ -1168,8 +1211,11 @@
       <c r="O16">
         <v>6</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P16">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>11</v>
       </c>
@@ -1215,8 +1261,11 @@
       <c r="O17">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>12</v>
       </c>
@@ -1262,8 +1311,11 @@
       <c r="O18">
         <v>8</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P18">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>13</v>
       </c>
@@ -1309,8 +1361,11 @@
       <c r="O19">
         <v>10</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P19">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>14</v>
       </c>
@@ -1356,8 +1411,11 @@
       <c r="O20">
         <v>8</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P20">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>15</v>
       </c>
@@ -1403,8 +1461,11 @@
       <c r="O21">
         <v>2</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P21">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>16</v>
       </c>
@@ -1450,8 +1511,11 @@
       <c r="O22" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P22">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>17</v>
       </c>
@@ -1497,8 +1561,11 @@
       <c r="O23">
         <v>5</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P23">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>18</v>
       </c>
@@ -1544,8 +1611,11 @@
       <c r="O24">
         <v>6</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P24">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>19</v>
       </c>
@@ -1591,8 +1661,11 @@
       <c r="O25">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P25">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>20</v>
       </c>
@@ -1638,8 +1711,11 @@
       <c r="O26">
         <v>5</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>21</v>
       </c>
@@ -1685,8 +1761,11 @@
       <c r="O27">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P27">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>22</v>
       </c>
@@ -1732,8 +1811,11 @@
       <c r="O28">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P28" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>23</v>
       </c>
@@ -1779,8 +1861,11 @@
       <c r="O29">
         <v>6</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P29">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>24</v>
       </c>
@@ -1807,6 +1892,9 @@
       </c>
       <c r="O30">
         <v>10</v>
+      </c>
+      <c r="P30">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
